--- a/IC-Simple-Gantt-Chart-Template.xlsx
+++ b/IC-Simple-Gantt-Chart-Template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9600" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9600" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="EXAMPLE - Gantt Chart" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="-Disclaimer-" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'BLANK - Gantt Chart'!$B$2:$BP$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'BLANK - Gantt Chart'!$B$2:$BP$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'EXAMPLE - Gantt Chart'!$B$3:$BP$35</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="122">
   <si>
     <t>DATE</t>
   </si>
@@ -310,16 +310,106 @@
     <t xml:space="preserve">Simple Gantt Chart Template </t>
   </si>
   <si>
-    <t>Subtask</t>
-  </si>
-  <si>
     <t>DapurKita</t>
   </si>
   <si>
     <t>Kuliner</t>
   </si>
   <si>
-    <t>Daging</t>
+    <t>Makanan</t>
+  </si>
+  <si>
+    <t>Identifikasi Stakeholder</t>
+  </si>
+  <si>
+    <t>System Analyst</t>
+  </si>
+  <si>
+    <t>Analisis Kebutuhan Fungsional</t>
+  </si>
+  <si>
+    <t>Analisis Kebutuhan Non Fungsional</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Penyusunan Dokumen SRS</t>
+  </si>
+  <si>
+    <t>Desain UI/UX</t>
+  </si>
+  <si>
+    <t>UI/UX Designer</t>
+  </si>
+  <si>
+    <t>Desain Database</t>
+  </si>
+  <si>
+    <t>Backend Developer</t>
+  </si>
+  <si>
+    <t>Fronted Development</t>
+  </si>
+  <si>
+    <t>Fronted Developer</t>
+  </si>
+  <si>
+    <t>Backend Development</t>
+  </si>
+  <si>
+    <t>Integrasi Sistem</t>
+  </si>
+  <si>
+    <t>Fullstack Developer</t>
+  </si>
+  <si>
+    <t>Testing (QA)</t>
+  </si>
+  <si>
+    <t>Bug Fixing</t>
+  </si>
+  <si>
+    <t>Deployment</t>
+  </si>
+  <si>
+    <t>Developer Team</t>
+  </si>
+  <si>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>DevOps Engineer</t>
   </si>
 </sst>
 </file>
@@ -441,7 +531,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,18 +606,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00BD32"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1161,7 +1239,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1324,8 +1402,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="4" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1391,7 +1467,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1421,13 +1497,13 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1451,15 +1527,28 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
@@ -1471,8 +1560,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <colors>
     <mruColors>
+      <color rgb="FFEAEEF3"/>
       <color rgb="FF01BD32"/>
-      <color rgb="FFEAEEF3"/>
       <color rgb="FF6A3AFF"/>
       <color rgb="FFEE57AD"/>
       <color rgb="FFFFC11D"/>
@@ -1752,7 +1841,7 @@
   <sheetData>
     <row r="1" spans="2:68" ht="197.1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:68" s="46" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="91" t="s">
         <v>86</v>
       </c>
       <c r="C2" s="47"/>
@@ -1774,56 +1863,56 @@
       <c r="S2" s="48"/>
     </row>
     <row r="3" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
     </row>
     <row r="4" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="97" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="97" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
-      <c r="G5" s="97"/>
-      <c r="H5" s="97"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
     </row>
     <row r="6" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="96"/>
-      <c r="D6" s="98">
-        <v>46114</v>
-      </c>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="96" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="96"/>
     </row>
     <row r="7" spans="2:68" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
@@ -1836,74 +1925,74 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="109" t="s">
+      <c r="I8" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="110"/>
-      <c r="S8" s="110"/>
-      <c r="T8" s="110"/>
-      <c r="U8" s="110"/>
-      <c r="V8" s="110"/>
-      <c r="W8" s="111"/>
-      <c r="X8" s="103" t="s">
+      <c r="J8" s="108"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108"/>
+      <c r="O8" s="108"/>
+      <c r="P8" s="108"/>
+      <c r="Q8" s="108"/>
+      <c r="R8" s="108"/>
+      <c r="S8" s="108"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="108"/>
+      <c r="V8" s="108"/>
+      <c r="W8" s="109"/>
+      <c r="X8" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="Y8" s="104"/>
-      <c r="Z8" s="104"/>
-      <c r="AA8" s="104"/>
-      <c r="AB8" s="104"/>
-      <c r="AC8" s="104"/>
-      <c r="AD8" s="104"/>
-      <c r="AE8" s="104"/>
-      <c r="AF8" s="104"/>
-      <c r="AG8" s="104"/>
-      <c r="AH8" s="104"/>
-      <c r="AI8" s="104"/>
-      <c r="AJ8" s="104"/>
-      <c r="AK8" s="104"/>
-      <c r="AL8" s="105"/>
-      <c r="AM8" s="106" t="s">
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="102"/>
+      <c r="AE8" s="102"/>
+      <c r="AF8" s="102"/>
+      <c r="AG8" s="102"/>
+      <c r="AH8" s="102"/>
+      <c r="AI8" s="102"/>
+      <c r="AJ8" s="102"/>
+      <c r="AK8" s="102"/>
+      <c r="AL8" s="103"/>
+      <c r="AM8" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="AN8" s="107"/>
-      <c r="AO8" s="107"/>
-      <c r="AP8" s="107"/>
-      <c r="AQ8" s="107"/>
-      <c r="AR8" s="107"/>
-      <c r="AS8" s="107"/>
-      <c r="AT8" s="107"/>
-      <c r="AU8" s="107"/>
-      <c r="AV8" s="107"/>
-      <c r="AW8" s="107"/>
-      <c r="AX8" s="107"/>
-      <c r="AY8" s="107"/>
-      <c r="AZ8" s="107"/>
-      <c r="BA8" s="108"/>
-      <c r="BB8" s="112" t="s">
+      <c r="AN8" s="105"/>
+      <c r="AO8" s="105"/>
+      <c r="AP8" s="105"/>
+      <c r="AQ8" s="105"/>
+      <c r="AR8" s="105"/>
+      <c r="AS8" s="105"/>
+      <c r="AT8" s="105"/>
+      <c r="AU8" s="105"/>
+      <c r="AV8" s="105"/>
+      <c r="AW8" s="105"/>
+      <c r="AX8" s="105"/>
+      <c r="AY8" s="105"/>
+      <c r="AZ8" s="105"/>
+      <c r="BA8" s="106"/>
+      <c r="BB8" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="BC8" s="113"/>
-      <c r="BD8" s="113"/>
-      <c r="BE8" s="113"/>
-      <c r="BF8" s="113"/>
-      <c r="BG8" s="113"/>
-      <c r="BH8" s="113"/>
-      <c r="BI8" s="113"/>
-      <c r="BJ8" s="113"/>
-      <c r="BK8" s="113"/>
-      <c r="BL8" s="113"/>
-      <c r="BM8" s="113"/>
-      <c r="BN8" s="113"/>
-      <c r="BO8" s="113"/>
-      <c r="BP8" s="114"/>
+      <c r="BC8" s="111"/>
+      <c r="BD8" s="111"/>
+      <c r="BE8" s="111"/>
+      <c r="BF8" s="111"/>
+      <c r="BG8" s="111"/>
+      <c r="BH8" s="111"/>
+      <c r="BI8" s="111"/>
+      <c r="BJ8" s="111"/>
+      <c r="BK8" s="111"/>
+      <c r="BL8" s="111"/>
+      <c r="BM8" s="111"/>
+      <c r="BN8" s="111"/>
+      <c r="BO8" s="111"/>
+      <c r="BP8" s="112"/>
     </row>
     <row r="9" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
@@ -1915,10 +2004,10 @@
       <c r="D9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="87" t="s">
+      <c r="E9" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="88" t="s">
+      <c r="F9" s="86" t="s">
         <v>81</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -1927,90 +2016,90 @@
       <c r="H9" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="121" t="s">
+      <c r="I9" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="119"/>
-      <c r="K9" s="119"/>
-      <c r="L9" s="119"/>
-      <c r="M9" s="119"/>
-      <c r="N9" s="119" t="s">
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="119"/>
-      <c r="P9" s="119"/>
-      <c r="Q9" s="119"/>
-      <c r="R9" s="119"/>
-      <c r="S9" s="119" t="s">
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="T9" s="119"/>
-      <c r="U9" s="119"/>
-      <c r="V9" s="119"/>
-      <c r="W9" s="120"/>
-      <c r="X9" s="100" t="s">
+      <c r="T9" s="117"/>
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="Y9" s="101"/>
-      <c r="Z9" s="101"/>
-      <c r="AA9" s="101"/>
-      <c r="AB9" s="101"/>
-      <c r="AC9" s="101" t="s">
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="99"/>
+      <c r="AC9" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AD9" s="101"/>
-      <c r="AE9" s="101"/>
-      <c r="AF9" s="101"/>
-      <c r="AG9" s="101"/>
-      <c r="AH9" s="101" t="s">
+      <c r="AD9" s="99"/>
+      <c r="AE9" s="99"/>
+      <c r="AF9" s="99"/>
+      <c r="AG9" s="99"/>
+      <c r="AH9" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="AI9" s="101"/>
-      <c r="AJ9" s="101"/>
-      <c r="AK9" s="101"/>
-      <c r="AL9" s="102"/>
-      <c r="AM9" s="94" t="s">
+      <c r="AI9" s="99"/>
+      <c r="AJ9" s="99"/>
+      <c r="AK9" s="99"/>
+      <c r="AL9" s="100"/>
+      <c r="AM9" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="AN9" s="95"/>
-      <c r="AO9" s="95"/>
-      <c r="AP9" s="95"/>
-      <c r="AQ9" s="95"/>
-      <c r="AR9" s="95" t="s">
+      <c r="AN9" s="93"/>
+      <c r="AO9" s="93"/>
+      <c r="AP9" s="93"/>
+      <c r="AQ9" s="93"/>
+      <c r="AR9" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="AS9" s="95"/>
-      <c r="AT9" s="95"/>
-      <c r="AU9" s="95"/>
-      <c r="AV9" s="95"/>
-      <c r="AW9" s="95" t="s">
+      <c r="AS9" s="93"/>
+      <c r="AT9" s="93"/>
+      <c r="AU9" s="93"/>
+      <c r="AV9" s="93"/>
+      <c r="AW9" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="AX9" s="95"/>
-      <c r="AY9" s="95"/>
-      <c r="AZ9" s="95"/>
-      <c r="BA9" s="115"/>
-      <c r="BB9" s="116" t="s">
+      <c r="AX9" s="93"/>
+      <c r="AY9" s="93"/>
+      <c r="AZ9" s="93"/>
+      <c r="BA9" s="113"/>
+      <c r="BB9" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="BC9" s="117"/>
-      <c r="BD9" s="117"/>
-      <c r="BE9" s="117"/>
-      <c r="BF9" s="117"/>
-      <c r="BG9" s="117" t="s">
+      <c r="BC9" s="115"/>
+      <c r="BD9" s="115"/>
+      <c r="BE9" s="115"/>
+      <c r="BF9" s="115"/>
+      <c r="BG9" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="BH9" s="117"/>
-      <c r="BI9" s="117"/>
-      <c r="BJ9" s="117"/>
-      <c r="BK9" s="117"/>
-      <c r="BL9" s="117" t="s">
+      <c r="BH9" s="115"/>
+      <c r="BI9" s="115"/>
+      <c r="BJ9" s="115"/>
+      <c r="BK9" s="115"/>
+      <c r="BL9" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="BM9" s="117"/>
-      <c r="BN9" s="117"/>
-      <c r="BO9" s="117"/>
-      <c r="BP9" s="118"/>
+      <c r="BM9" s="115"/>
+      <c r="BN9" s="115"/>
+      <c r="BO9" s="115"/>
+      <c r="BP9" s="116"/>
     </row>
     <row r="10" spans="2:68" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
@@ -2022,10 +2111,10 @@
       <c r="D10" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="89" t="s">
+      <c r="E10" s="87" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="90" t="s">
+      <c r="F10" s="88" t="s">
         <v>74</v>
       </c>
       <c r="G10" s="11" t="s">
@@ -2223,8 +2312,8 @@
         <v>32</v>
       </c>
       <c r="D11" s="51"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="75"/>
       <c r="G11" s="52" t="str">
         <f>IF(F11-E11=0,"",F11-E11)</f>
         <v/>
@@ -2301,13 +2390,13 @@
       <c r="D12" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="78">
         <v>48650</v>
       </c>
-      <c r="F12" s="83">
+      <c r="F12" s="81">
         <v>48653</v>
       </c>
-      <c r="G12" s="85">
+      <c r="G12" s="83">
         <f t="shared" ref="G12:G35" si="0">IF(F12-E12=0,"",F12-E12)</f>
         <v>3</v>
       </c>
@@ -2385,13 +2474,13 @@
       <c r="D13" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="80">
+      <c r="E13" s="78">
         <v>48653</v>
       </c>
-      <c r="F13" s="83">
+      <c r="F13" s="81">
         <v>48654</v>
       </c>
-      <c r="G13" s="85">
+      <c r="G13" s="83">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2469,13 +2558,13 @@
       <c r="D14" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="80">
+      <c r="E14" s="78">
         <v>48653</v>
       </c>
-      <c r="F14" s="83">
+      <c r="F14" s="81">
         <v>48659</v>
       </c>
-      <c r="G14" s="85">
+      <c r="G14" s="83">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2553,13 +2642,13 @@
       <c r="D15" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="80">
+      <c r="E15" s="78">
         <v>48654</v>
       </c>
-      <c r="F15" s="83">
+      <c r="F15" s="81">
         <v>48660</v>
       </c>
-      <c r="G15" s="85">
+      <c r="G15" s="83">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -2637,13 +2726,13 @@
       <c r="D16" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="80">
+      <c r="E16" s="78">
         <v>45002</v>
       </c>
-      <c r="F16" s="83">
+      <c r="F16" s="81">
         <v>48660</v>
       </c>
-      <c r="G16" s="85">
+      <c r="G16" s="83">
         <f t="shared" si="0"/>
         <v>3658</v>
       </c>
@@ -2721,13 +2810,13 @@
       <c r="D17" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="80">
+      <c r="E17" s="78">
         <v>48656</v>
       </c>
-      <c r="F17" s="83">
+      <c r="F17" s="81">
         <v>48660</v>
       </c>
-      <c r="G17" s="85">
+      <c r="G17" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2805,13 +2894,13 @@
       <c r="D18" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="80">
+      <c r="E18" s="78">
         <v>48661</v>
       </c>
-      <c r="F18" s="83">
+      <c r="F18" s="81">
         <v>48661</v>
       </c>
-      <c r="G18" s="85" t="str">
+      <c r="G18" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2832,7 +2921,7 @@
       <c r="T18" s="26"/>
       <c r="U18" s="26"/>
       <c r="V18" s="26"/>
-      <c r="W18" s="76"/>
+      <c r="W18" s="74"/>
       <c r="X18" s="25"/>
       <c r="Y18" s="26"/>
       <c r="Z18" s="26"/>
@@ -2887,8 +2976,8 @@
         <v>47</v>
       </c>
       <c r="D19" s="59"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="78"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="76"/>
       <c r="G19" s="60" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2965,13 +3054,13 @@
       <c r="D20" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="80">
+      <c r="E20" s="78">
         <v>48662</v>
       </c>
-      <c r="F20" s="83">
+      <c r="F20" s="81">
         <v>48666</v>
       </c>
-      <c r="G20" s="85">
+      <c r="G20" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3049,13 +3138,13 @@
       <c r="D21" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="80">
+      <c r="E21" s="78">
         <v>48667</v>
       </c>
-      <c r="F21" s="83">
+      <c r="F21" s="81">
         <v>48671</v>
       </c>
-      <c r="G21" s="85">
+      <c r="G21" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3133,9 +3222,9 @@
       <c r="D22" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="80"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="85" t="str">
+      <c r="E22" s="78"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3213,9 +3302,9 @@
       <c r="D23" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="80"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="85" t="str">
+      <c r="E23" s="78"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3291,8 +3380,8 @@
         <v>52</v>
       </c>
       <c r="D24" s="59"/>
-      <c r="E24" s="81"/>
-      <c r="F24" s="78"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="76"/>
       <c r="G24" s="60" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3369,9 +3458,9 @@
       <c r="D25" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="80"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="85" t="str">
+      <c r="E25" s="78"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3449,9 +3538,9 @@
       <c r="D26" s="55" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="85" t="str">
+      <c r="E26" s="78"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3529,9 +3618,9 @@
       <c r="D27" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="80"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="85" t="str">
+      <c r="E27" s="78"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3609,9 +3698,9 @@
       <c r="D28" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="E28" s="80"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="85" t="str">
+      <c r="E28" s="78"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3691,9 +3780,9 @@
       <c r="D29" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="E29" s="80"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="85" t="str">
+      <c r="E29" s="78"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3771,9 +3860,9 @@
       <c r="D30" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="80"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="85" t="str">
+      <c r="E30" s="78"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -3849,8 +3938,8 @@
         <v>63</v>
       </c>
       <c r="D31" s="59"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="78"/>
+      <c r="E31" s="79"/>
+      <c r="F31" s="76"/>
       <c r="G31" s="60" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3927,9 +4016,9 @@
       <c r="D32" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="80"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="85" t="str">
+      <c r="E32" s="78"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4007,9 +4096,9 @@
       <c r="D33" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="E33" s="80"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="85" t="str">
+      <c r="E33" s="78"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4087,9 +4176,9 @@
       <c r="D34" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="80"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="85" t="str">
+      <c r="E34" s="78"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="83" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4167,9 +4256,9 @@
       <c r="D35" s="63" t="s">
         <v>45</v>
       </c>
-      <c r="E35" s="82"/>
-      <c r="F35" s="84"/>
-      <c r="G35" s="86" t="str">
+      <c r="E35" s="80"/>
+      <c r="F35" s="82"/>
+      <c r="G35" s="84" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -4238,75 +4327,75 @@
       <c r="BP35" s="40"/>
     </row>
     <row r="37" spans="2:68" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="99" t="s">
+      <c r="B37" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="99"/>
-      <c r="K37" s="99"/>
-      <c r="L37" s="99"/>
-      <c r="M37" s="99"/>
-      <c r="N37" s="99"/>
-      <c r="O37" s="99"/>
-      <c r="P37" s="99"/>
-      <c r="Q37" s="99"/>
-      <c r="R37" s="99"/>
-      <c r="S37" s="99"/>
-      <c r="T37" s="99"/>
-      <c r="U37" s="99"/>
-      <c r="V37" s="99"/>
-      <c r="W37" s="99"/>
-      <c r="X37" s="99"/>
-      <c r="Y37" s="99"/>
-      <c r="Z37" s="99"/>
-      <c r="AA37" s="99"/>
-      <c r="AB37" s="99"/>
-      <c r="AC37" s="99"/>
-      <c r="AD37" s="99"/>
-      <c r="AE37" s="99"/>
-      <c r="AF37" s="99"/>
-      <c r="AG37" s="99"/>
-      <c r="AH37" s="99"/>
-      <c r="AI37" s="99"/>
-      <c r="AJ37" s="99"/>
-      <c r="AK37" s="99"/>
-      <c r="AL37" s="99"/>
-      <c r="AM37" s="99"/>
-      <c r="AN37" s="99"/>
-      <c r="AO37" s="99"/>
-      <c r="AP37" s="99"/>
-      <c r="AQ37" s="99"/>
-      <c r="AR37" s="99"/>
-      <c r="AS37" s="99"/>
-      <c r="AT37" s="99"/>
-      <c r="AU37" s="99"/>
-      <c r="AV37" s="99"/>
-      <c r="AW37" s="99"/>
-      <c r="AX37" s="99"/>
-      <c r="AY37" s="99"/>
-      <c r="AZ37" s="99"/>
-      <c r="BA37" s="99"/>
-      <c r="BB37" s="99"/>
-      <c r="BC37" s="99"/>
-      <c r="BD37" s="99"/>
-      <c r="BE37" s="99"/>
-      <c r="BF37" s="99"/>
-      <c r="BG37" s="99"/>
-      <c r="BH37" s="99"/>
-      <c r="BI37" s="99"/>
-      <c r="BJ37" s="99"/>
-      <c r="BK37" s="99"/>
-      <c r="BL37" s="99"/>
-      <c r="BM37" s="99"/>
-      <c r="BN37" s="99"/>
-      <c r="BO37" s="99"/>
-      <c r="BP37" s="99"/>
+      <c r="C37" s="97"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="97"/>
+      <c r="F37" s="97"/>
+      <c r="G37" s="97"/>
+      <c r="H37" s="97"/>
+      <c r="I37" s="97"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="97"/>
+      <c r="M37" s="97"/>
+      <c r="N37" s="97"/>
+      <c r="O37" s="97"/>
+      <c r="P37" s="97"/>
+      <c r="Q37" s="97"/>
+      <c r="R37" s="97"/>
+      <c r="S37" s="97"/>
+      <c r="T37" s="97"/>
+      <c r="U37" s="97"/>
+      <c r="V37" s="97"/>
+      <c r="W37" s="97"/>
+      <c r="X37" s="97"/>
+      <c r="Y37" s="97"/>
+      <c r="Z37" s="97"/>
+      <c r="AA37" s="97"/>
+      <c r="AB37" s="97"/>
+      <c r="AC37" s="97"/>
+      <c r="AD37" s="97"/>
+      <c r="AE37" s="97"/>
+      <c r="AF37" s="97"/>
+      <c r="AG37" s="97"/>
+      <c r="AH37" s="97"/>
+      <c r="AI37" s="97"/>
+      <c r="AJ37" s="97"/>
+      <c r="AK37" s="97"/>
+      <c r="AL37" s="97"/>
+      <c r="AM37" s="97"/>
+      <c r="AN37" s="97"/>
+      <c r="AO37" s="97"/>
+      <c r="AP37" s="97"/>
+      <c r="AQ37" s="97"/>
+      <c r="AR37" s="97"/>
+      <c r="AS37" s="97"/>
+      <c r="AT37" s="97"/>
+      <c r="AU37" s="97"/>
+      <c r="AV37" s="97"/>
+      <c r="AW37" s="97"/>
+      <c r="AX37" s="97"/>
+      <c r="AY37" s="97"/>
+      <c r="AZ37" s="97"/>
+      <c r="BA37" s="97"/>
+      <c r="BB37" s="97"/>
+      <c r="BC37" s="97"/>
+      <c r="BD37" s="97"/>
+      <c r="BE37" s="97"/>
+      <c r="BF37" s="97"/>
+      <c r="BG37" s="97"/>
+      <c r="BH37" s="97"/>
+      <c r="BI37" s="97"/>
+      <c r="BJ37" s="97"/>
+      <c r="BK37" s="97"/>
+      <c r="BL37" s="97"/>
+      <c r="BM37" s="97"/>
+      <c r="BN37" s="97"/>
+      <c r="BO37" s="97"/>
+      <c r="BP37" s="97"/>
     </row>
     <row r="43" spans="2:68" ht="19.5" x14ac:dyDescent="0.3">
       <c r="C43" s="3"/>
@@ -4392,7 +4481,7 @@
     <tabColor theme="3" tint="0.79998168889431442"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:BP41"/>
+  <dimension ref="B1:BP28"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -4405,7 +4494,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:68" s="46" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="91" t="s">
         <v>87</v>
       </c>
       <c r="C1" s="47"/>
@@ -4427,56 +4516,56 @@
       <c r="S1" s="48"/>
     </row>
     <row r="2" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="96"/>
-      <c r="D2" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="97"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
     </row>
     <row r="3" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="97"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
     </row>
     <row r="4" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="2:68" s="1" customFormat="1" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="96">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
     </row>
     <row r="6" spans="2:68" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
@@ -4489,74 +4578,74 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="109" t="s">
+      <c r="I7" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="110"/>
-      <c r="T7" s="110"/>
-      <c r="U7" s="110"/>
-      <c r="V7" s="110"/>
-      <c r="W7" s="111"/>
-      <c r="X7" s="103" t="s">
+      <c r="J7" s="108"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="108"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="108"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="108"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="108"/>
+      <c r="W7" s="109"/>
+      <c r="X7" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="Y7" s="104"/>
-      <c r="Z7" s="104"/>
-      <c r="AA7" s="104"/>
-      <c r="AB7" s="104"/>
-      <c r="AC7" s="104"/>
-      <c r="AD7" s="104"/>
-      <c r="AE7" s="104"/>
-      <c r="AF7" s="104"/>
-      <c r="AG7" s="104"/>
-      <c r="AH7" s="104"/>
-      <c r="AI7" s="104"/>
-      <c r="AJ7" s="104"/>
-      <c r="AK7" s="104"/>
-      <c r="AL7" s="105"/>
-      <c r="AM7" s="106" t="s">
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="102"/>
+      <c r="AA7" s="102"/>
+      <c r="AB7" s="102"/>
+      <c r="AC7" s="102"/>
+      <c r="AD7" s="102"/>
+      <c r="AE7" s="102"/>
+      <c r="AF7" s="102"/>
+      <c r="AG7" s="102"/>
+      <c r="AH7" s="102"/>
+      <c r="AI7" s="102"/>
+      <c r="AJ7" s="102"/>
+      <c r="AK7" s="102"/>
+      <c r="AL7" s="103"/>
+      <c r="AM7" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="AN7" s="107"/>
-      <c r="AO7" s="107"/>
-      <c r="AP7" s="107"/>
-      <c r="AQ7" s="107"/>
-      <c r="AR7" s="107"/>
-      <c r="AS7" s="107"/>
-      <c r="AT7" s="107"/>
-      <c r="AU7" s="107"/>
-      <c r="AV7" s="107"/>
-      <c r="AW7" s="107"/>
-      <c r="AX7" s="107"/>
-      <c r="AY7" s="107"/>
-      <c r="AZ7" s="107"/>
-      <c r="BA7" s="108"/>
-      <c r="BB7" s="112" t="s">
+      <c r="AN7" s="105"/>
+      <c r="AO7" s="105"/>
+      <c r="AP7" s="105"/>
+      <c r="AQ7" s="105"/>
+      <c r="AR7" s="105"/>
+      <c r="AS7" s="105"/>
+      <c r="AT7" s="105"/>
+      <c r="AU7" s="105"/>
+      <c r="AV7" s="105"/>
+      <c r="AW7" s="105"/>
+      <c r="AX7" s="105"/>
+      <c r="AY7" s="105"/>
+      <c r="AZ7" s="105"/>
+      <c r="BA7" s="106"/>
+      <c r="BB7" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="BC7" s="113"/>
-      <c r="BD7" s="113"/>
-      <c r="BE7" s="113"/>
-      <c r="BF7" s="113"/>
-      <c r="BG7" s="113"/>
-      <c r="BH7" s="113"/>
-      <c r="BI7" s="113"/>
-      <c r="BJ7" s="113"/>
-      <c r="BK7" s="113"/>
-      <c r="BL7" s="113"/>
-      <c r="BM7" s="113"/>
-      <c r="BN7" s="113"/>
-      <c r="BO7" s="113"/>
-      <c r="BP7" s="114"/>
+      <c r="BC7" s="111"/>
+      <c r="BD7" s="111"/>
+      <c r="BE7" s="111"/>
+      <c r="BF7" s="111"/>
+      <c r="BG7" s="111"/>
+      <c r="BH7" s="111"/>
+      <c r="BI7" s="111"/>
+      <c r="BJ7" s="111"/>
+      <c r="BK7" s="111"/>
+      <c r="BL7" s="111"/>
+      <c r="BM7" s="111"/>
+      <c r="BN7" s="111"/>
+      <c r="BO7" s="111"/>
+      <c r="BP7" s="112"/>
     </row>
     <row r="8" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
@@ -4568,10 +4657,10 @@
       <c r="D8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="87" t="s">
+      <c r="E8" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="86" t="s">
         <v>7</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -4580,90 +4669,90 @@
       <c r="H8" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="121" t="s">
+      <c r="I8" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="119"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="119"/>
-      <c r="N8" s="119" t="s">
+      <c r="J8" s="117"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="119"/>
-      <c r="R8" s="119"/>
-      <c r="S8" s="119" t="s">
+      <c r="O8" s="117"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="117"/>
+      <c r="S8" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="T8" s="119"/>
-      <c r="U8" s="119"/>
-      <c r="V8" s="119"/>
-      <c r="W8" s="120"/>
-      <c r="X8" s="100" t="s">
+      <c r="T8" s="117"/>
+      <c r="U8" s="117"/>
+      <c r="V8" s="117"/>
+      <c r="W8" s="118"/>
+      <c r="X8" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="Y8" s="101"/>
-      <c r="Z8" s="101"/>
-      <c r="AA8" s="101"/>
-      <c r="AB8" s="101"/>
-      <c r="AC8" s="101" t="s">
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AA8" s="99"/>
+      <c r="AB8" s="99"/>
+      <c r="AC8" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="AD8" s="101"/>
-      <c r="AE8" s="101"/>
-      <c r="AF8" s="101"/>
-      <c r="AG8" s="101"/>
-      <c r="AH8" s="101" t="s">
+      <c r="AD8" s="99"/>
+      <c r="AE8" s="99"/>
+      <c r="AF8" s="99"/>
+      <c r="AG8" s="99"/>
+      <c r="AH8" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="AI8" s="101"/>
-      <c r="AJ8" s="101"/>
-      <c r="AK8" s="101"/>
-      <c r="AL8" s="102"/>
-      <c r="AM8" s="94" t="s">
+      <c r="AI8" s="99"/>
+      <c r="AJ8" s="99"/>
+      <c r="AK8" s="99"/>
+      <c r="AL8" s="100"/>
+      <c r="AM8" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="AN8" s="95"/>
-      <c r="AO8" s="95"/>
-      <c r="AP8" s="95"/>
-      <c r="AQ8" s="95"/>
-      <c r="AR8" s="95" t="s">
+      <c r="AN8" s="93"/>
+      <c r="AO8" s="93"/>
+      <c r="AP8" s="93"/>
+      <c r="AQ8" s="93"/>
+      <c r="AR8" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="AS8" s="95"/>
-      <c r="AT8" s="95"/>
-      <c r="AU8" s="95"/>
-      <c r="AV8" s="95"/>
-      <c r="AW8" s="95" t="s">
+      <c r="AS8" s="93"/>
+      <c r="AT8" s="93"/>
+      <c r="AU8" s="93"/>
+      <c r="AV8" s="93"/>
+      <c r="AW8" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="AX8" s="95"/>
-      <c r="AY8" s="95"/>
-      <c r="AZ8" s="95"/>
-      <c r="BA8" s="115"/>
-      <c r="BB8" s="116" t="s">
+      <c r="AX8" s="93"/>
+      <c r="AY8" s="93"/>
+      <c r="AZ8" s="93"/>
+      <c r="BA8" s="113"/>
+      <c r="BB8" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="BC8" s="117"/>
-      <c r="BD8" s="117"/>
-      <c r="BE8" s="117"/>
-      <c r="BF8" s="117"/>
-      <c r="BG8" s="117" t="s">
+      <c r="BC8" s="115"/>
+      <c r="BD8" s="115"/>
+      <c r="BE8" s="115"/>
+      <c r="BF8" s="115"/>
+      <c r="BG8" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="BH8" s="117"/>
-      <c r="BI8" s="117"/>
-      <c r="BJ8" s="117"/>
-      <c r="BK8" s="117"/>
-      <c r="BL8" s="117" t="s">
+      <c r="BH8" s="115"/>
+      <c r="BI8" s="115"/>
+      <c r="BJ8" s="115"/>
+      <c r="BK8" s="115"/>
+      <c r="BL8" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="BM8" s="117"/>
-      <c r="BN8" s="117"/>
-      <c r="BO8" s="117"/>
-      <c r="BP8" s="118"/>
+      <c r="BM8" s="115"/>
+      <c r="BN8" s="115"/>
+      <c r="BO8" s="115"/>
+      <c r="BP8" s="116"/>
     </row>
     <row r="9" spans="2:68" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="9" t="s">
@@ -4675,10 +4764,10 @@
       <c r="D9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="89" t="s">
+      <c r="E9" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="90" t="s">
+      <c r="F9" s="88" t="s">
         <v>0</v>
       </c>
       <c r="G9" s="11" t="s">
@@ -4868,26 +4957,33 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:68" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:68" ht="29.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B10" s="49">
         <v>1</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="52" t="str">
-        <f>IF(F10-E10=0,"",F10-E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="69"/>
+        <v>91</v>
+      </c>
+      <c r="D10" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="77">
+        <v>46143</v>
+      </c>
+      <c r="F10" s="75">
+        <v>46144</v>
+      </c>
+      <c r="G10" s="52">
+        <v>2</v>
+      </c>
+      <c r="H10" s="70">
+        <v>1</v>
+      </c>
       <c r="I10" s="64"/>
       <c r="J10" s="22"/>
       <c r="K10" s="22"/>
       <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
+      <c r="M10" s="73"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
@@ -4944,30 +5040,36 @@
       <c r="BO10" s="22"/>
       <c r="BP10" s="24"/>
     </row>
-    <row r="11" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="C11" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="55"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="85" t="str">
-        <f t="shared" ref="G11:G34" si="0">IF(F11-E11=0,"",F11-E11)</f>
-        <v/>
+    <row r="11" spans="2:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="121" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="79">
+        <v>46145</v>
+      </c>
+      <c r="F11" s="76">
+        <v>46147</v>
+      </c>
+      <c r="G11" s="60">
+        <f t="shared" ref="G11:G21" si="0">IF(F11-E11=0,"",F11-E11)</f>
+        <v>2</v>
       </c>
       <c r="H11" s="70">
         <v>1</v>
       </c>
       <c r="I11" s="65"/>
-      <c r="J11" s="73"/>
+      <c r="J11" s="124"/>
       <c r="K11" s="26"/>
       <c r="L11" s="26"/>
       <c r="M11" s="26"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
       <c r="P11" s="27"/>
       <c r="Q11" s="27"/>
       <c r="R11" s="27"/>
@@ -5022,30 +5124,36 @@
       <c r="BO11" s="26"/>
       <c r="BP11" s="31"/>
     </row>
-    <row r="12" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:68" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="53" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="85" t="str">
+        <v>96</v>
+      </c>
+      <c r="C12" s="122" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="79">
+        <v>46145</v>
+      </c>
+      <c r="F12" s="76">
+        <v>46147</v>
+      </c>
+      <c r="G12" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H12" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="65"/>
       <c r="J12" s="26"/>
       <c r="K12" s="26"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="73"/>
       <c r="P12" s="27"/>
       <c r="Q12" s="27"/>
       <c r="R12" s="27"/>
@@ -5100,22 +5208,28 @@
       <c r="BO12" s="26"/>
       <c r="BP12" s="31"/>
     </row>
-    <row r="13" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="53">
-        <v>1.2</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="55"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="85" t="str">
+    <row r="13" spans="2:68" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="120" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="79">
+        <v>46148</v>
+      </c>
+      <c r="F13" s="76">
+        <v>46150</v>
+      </c>
+      <c r="G13" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H13" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="65"/>
       <c r="J13" s="26"/>
@@ -5124,9 +5238,9 @@
       <c r="M13" s="26"/>
       <c r="N13" s="27"/>
       <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="73"/>
       <c r="S13" s="26"/>
       <c r="T13" s="26"/>
       <c r="U13" s="26"/>
@@ -5179,21 +5293,27 @@
       <c r="BP13" s="31"/>
     </row>
     <row r="14" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="53">
-        <v>1.3</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="85" t="str">
+      <c r="B14" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="121" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="79">
+        <v>46151</v>
+      </c>
+      <c r="F14" s="76">
+        <v>46154</v>
+      </c>
+      <c r="G14" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="H14" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="65"/>
       <c r="J14" s="26"/>
@@ -5205,8 +5325,8 @@
       <c r="P14" s="27"/>
       <c r="Q14" s="27"/>
       <c r="R14" s="27"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="26"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
       <c r="U14" s="26"/>
       <c r="V14" s="26"/>
       <c r="W14" s="28"/>
@@ -5256,22 +5376,28 @@
       <c r="BO14" s="26"/>
       <c r="BP14" s="31"/>
     </row>
-    <row r="15" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="53">
-        <v>1.4</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="85" t="str">
+    <row r="15" spans="2:68" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="121" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="79">
+        <v>46151</v>
+      </c>
+      <c r="F15" s="76">
+        <v>46153</v>
+      </c>
+      <c r="G15" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H15" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="65"/>
       <c r="J15" s="26"/>
@@ -5283,7 +5409,7 @@
       <c r="P15" s="27"/>
       <c r="Q15" s="27"/>
       <c r="R15" s="27"/>
-      <c r="S15" s="26"/>
+      <c r="S15" s="73"/>
       <c r="T15" s="26"/>
       <c r="U15" s="26"/>
       <c r="V15" s="26"/>
@@ -5334,22 +5460,28 @@
       <c r="BO15" s="26"/>
       <c r="BP15" s="31"/>
     </row>
-    <row r="16" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="53">
-        <v>1.5</v>
-      </c>
-      <c r="C16" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="85" t="str">
+    <row r="16" spans="2:68" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="123" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="79">
+        <v>46155</v>
+      </c>
+      <c r="F16" s="76">
+        <v>46162</v>
+      </c>
+      <c r="G16" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H16" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="65"/>
       <c r="J16" s="26"/>
@@ -5362,10 +5494,10 @@
       <c r="Q16" s="27"/>
       <c r="R16" s="27"/>
       <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="26"/>
-      <c r="V16" s="26"/>
-      <c r="W16" s="28"/>
+      <c r="T16" s="73"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
       <c r="X16" s="25"/>
       <c r="Y16" s="26"/>
       <c r="Z16" s="26"/>
@@ -5412,22 +5544,28 @@
       <c r="BO16" s="26"/>
       <c r="BP16" s="31"/>
     </row>
-    <row r="17" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53">
-        <v>1.6</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="85" t="str">
+    <row r="17" spans="2:68" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="121" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="123" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="79">
+        <v>46155</v>
+      </c>
+      <c r="F17" s="76">
+        <v>46162</v>
+      </c>
+      <c r="G17" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="H17" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="65"/>
       <c r="J17" s="26"/>
@@ -5444,9 +5582,9 @@
       <c r="U17" s="26"/>
       <c r="V17" s="26"/>
       <c r="W17" s="28"/>
-      <c r="X17" s="25"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
       <c r="AC17" s="29"/>
@@ -5490,21 +5628,29 @@
       <c r="BO17" s="26"/>
       <c r="BP17" s="31"/>
     </row>
-    <row r="18" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="53">
+    <row r="18" spans="2:68" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="D18" s="123" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="79">
+        <v>46163</v>
+      </c>
+      <c r="F18" s="76">
+        <v>46165</v>
+      </c>
+      <c r="G18" s="60">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C18" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H18" s="71"/>
+      <c r="H18" s="70">
+        <v>1</v>
+      </c>
       <c r="I18" s="64"/>
       <c r="J18" s="22"/>
       <c r="K18" s="22"/>
@@ -5523,8 +5669,8 @@
       <c r="X18" s="21"/>
       <c r="Y18" s="22"/>
       <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
       <c r="AC18" s="22"/>
       <c r="AD18" s="22"/>
       <c r="AE18" s="22"/>
@@ -5567,21 +5713,27 @@
       <c r="BP18" s="24"/>
     </row>
     <row r="19" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="53">
-        <v>2.1</v>
-      </c>
-      <c r="C19" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" s="55"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="85" t="str">
+      <c r="B19" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="121" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="79">
+        <v>46166</v>
+      </c>
+      <c r="F19" s="76">
+        <v>46168</v>
+      </c>
+      <c r="G19" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="H19" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="65"/>
       <c r="J19" s="26"/>
@@ -5599,12 +5751,12 @@
       <c r="V19" s="26"/>
       <c r="W19" s="28"/>
       <c r="X19" s="25"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="26"/>
+      <c r="Y19" s="124"/>
+      <c r="Z19" s="124"/>
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
-      <c r="AC19" s="29"/>
-      <c r="AD19" s="29"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
       <c r="AE19" s="29"/>
       <c r="AF19" s="29"/>
       <c r="AG19" s="29"/>
@@ -5644,22 +5796,28 @@
       <c r="BO19" s="26"/>
       <c r="BP19" s="31"/>
     </row>
-    <row r="20" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="53">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="C20" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="55"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="85" t="str">
+    <row r="20" spans="2:68" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="121" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="79">
+        <v>46169</v>
+      </c>
+      <c r="F20" s="76">
+        <v>46170</v>
+      </c>
+      <c r="G20" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H20" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="65"/>
       <c r="J20" s="26"/>
@@ -5683,8 +5841,8 @@
       <c r="AB20" s="26"/>
       <c r="AC20" s="29"/>
       <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="33"/>
       <c r="AG20" s="29"/>
       <c r="AH20" s="26"/>
       <c r="AI20" s="26"/>
@@ -5722,22 +5880,28 @@
       <c r="BO20" s="26"/>
       <c r="BP20" s="31"/>
     </row>
-    <row r="21" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="85" t="str">
+    <row r="21" spans="2:68" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="121" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="123" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="79">
+        <v>46171</v>
+      </c>
+      <c r="F21" s="76">
+        <v>46172</v>
+      </c>
+      <c r="G21" s="60">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H21" s="70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="65"/>
       <c r="J21" s="26"/>
@@ -5763,7 +5927,7 @@
       <c r="AD21" s="29"/>
       <c r="AE21" s="29"/>
       <c r="AF21" s="29"/>
-      <c r="AG21" s="29"/>
+      <c r="AG21" s="33"/>
       <c r="AH21" s="26"/>
       <c r="AI21" s="26"/>
       <c r="AJ21" s="26"/>
@@ -5800,1020 +5964,8 @@
       <c r="BO21" s="26"/>
       <c r="BP21" s="31"/>
     </row>
-    <row r="22" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="53">
-        <v>2.4</v>
-      </c>
-      <c r="C22" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H22" s="70">
-        <v>0</v>
-      </c>
-      <c r="I22" s="65"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="26"/>
-      <c r="V22" s="26"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
-      <c r="AB22" s="26"/>
-      <c r="AC22" s="29"/>
-      <c r="AD22" s="29"/>
-      <c r="AE22" s="29"/>
-      <c r="AF22" s="29"/>
-      <c r="AG22" s="29"/>
-      <c r="AH22" s="26"/>
-      <c r="AI22" s="26"/>
-      <c r="AJ22" s="26"/>
-      <c r="AK22" s="26"/>
-      <c r="AL22" s="28"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="26"/>
-      <c r="AO22" s="26"/>
-      <c r="AP22" s="26"/>
-      <c r="AQ22" s="26"/>
-      <c r="AR22" s="44"/>
-      <c r="AS22" s="44"/>
-      <c r="AT22" s="44"/>
-      <c r="AU22" s="44"/>
-      <c r="AV22" s="44"/>
-      <c r="AW22" s="26"/>
-      <c r="AX22" s="26"/>
-      <c r="AY22" s="26"/>
-      <c r="AZ22" s="26"/>
-      <c r="BA22" s="28"/>
-      <c r="BB22" s="25"/>
-      <c r="BC22" s="26"/>
-      <c r="BD22" s="26"/>
-      <c r="BE22" s="26"/>
-      <c r="BF22" s="26"/>
-      <c r="BG22" s="30"/>
-      <c r="BH22" s="30"/>
-      <c r="BI22" s="30"/>
-      <c r="BJ22" s="30"/>
-      <c r="BK22" s="30"/>
-      <c r="BL22" s="26"/>
-      <c r="BM22" s="26"/>
-      <c r="BN22" s="26"/>
-      <c r="BO22" s="26"/>
-      <c r="BP22" s="31"/>
-    </row>
-    <row r="23" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="53">
-        <v>3</v>
-      </c>
-      <c r="C23" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H23" s="71"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="23"/>
-      <c r="X23" s="21"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="22"/>
-      <c r="AL23" s="23"/>
-      <c r="AM23" s="21"/>
-      <c r="AN23" s="22"/>
-      <c r="AO23" s="22"/>
-      <c r="AP23" s="22"/>
-      <c r="AQ23" s="22"/>
-      <c r="AR23" s="22"/>
-      <c r="AS23" s="22"/>
-      <c r="AT23" s="22"/>
-      <c r="AU23" s="22"/>
-      <c r="AV23" s="22"/>
-      <c r="AW23" s="22"/>
-      <c r="AX23" s="22"/>
-      <c r="AY23" s="22"/>
-      <c r="AZ23" s="22"/>
-      <c r="BA23" s="23"/>
-      <c r="BB23" s="21"/>
-      <c r="BC23" s="22"/>
-      <c r="BD23" s="22"/>
-      <c r="BE23" s="22"/>
-      <c r="BF23" s="22"/>
-      <c r="BG23" s="22"/>
-      <c r="BH23" s="22"/>
-      <c r="BI23" s="22"/>
-      <c r="BJ23" s="22"/>
-      <c r="BK23" s="22"/>
-      <c r="BL23" s="22"/>
-      <c r="BM23" s="22"/>
-      <c r="BN23" s="22"/>
-      <c r="BO23" s="22"/>
-      <c r="BP23" s="24"/>
-    </row>
-    <row r="24" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="53">
-        <v>3.1</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H24" s="70">
-        <v>0</v>
-      </c>
-      <c r="I24" s="65"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="26"/>
-      <c r="V24" s="26"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
-      <c r="AB24" s="26"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
-      <c r="AE24" s="29"/>
-      <c r="AF24" s="29"/>
-      <c r="AG24" s="29"/>
-      <c r="AH24" s="26"/>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="26"/>
-      <c r="AK24" s="26"/>
-      <c r="AL24" s="28"/>
-      <c r="AM24" s="25"/>
-      <c r="AN24" s="74"/>
-      <c r="AO24" s="26"/>
-      <c r="AP24" s="26"/>
-      <c r="AQ24" s="26"/>
-      <c r="AR24" s="44"/>
-      <c r="AS24" s="44"/>
-      <c r="AT24" s="44"/>
-      <c r="AU24" s="44"/>
-      <c r="AV24" s="44"/>
-      <c r="AW24" s="26"/>
-      <c r="AX24" s="26"/>
-      <c r="AY24" s="26"/>
-      <c r="AZ24" s="26"/>
-      <c r="BA24" s="28"/>
-      <c r="BB24" s="25"/>
-      <c r="BC24" s="26"/>
-      <c r="BD24" s="26"/>
-      <c r="BE24" s="26"/>
-      <c r="BF24" s="26"/>
-      <c r="BG24" s="30"/>
-      <c r="BH24" s="30"/>
-      <c r="BI24" s="30"/>
-      <c r="BJ24" s="30"/>
-      <c r="BK24" s="30"/>
-      <c r="BL24" s="26"/>
-      <c r="BM24" s="26"/>
-      <c r="BN24" s="26"/>
-      <c r="BO24" s="26"/>
-      <c r="BP24" s="31"/>
-    </row>
-    <row r="25" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="53">
-        <v>3.2</v>
-      </c>
-      <c r="C25" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="55"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H25" s="70">
-        <v>0</v>
-      </c>
-      <c r="I25" s="65"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="26"/>
-      <c r="T25" s="26"/>
-      <c r="U25" s="26"/>
-      <c r="V25" s="26"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="25"/>
-      <c r="Y25" s="26"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="26"/>
-      <c r="AB25" s="26"/>
-      <c r="AC25" s="29"/>
-      <c r="AD25" s="29"/>
-      <c r="AE25" s="29"/>
-      <c r="AF25" s="29"/>
-      <c r="AG25" s="29"/>
-      <c r="AH25" s="26"/>
-      <c r="AI25" s="26"/>
-      <c r="AJ25" s="26"/>
-      <c r="AK25" s="26"/>
-      <c r="AL25" s="28"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="26"/>
-      <c r="AO25" s="26"/>
-      <c r="AP25" s="26"/>
-      <c r="AQ25" s="26"/>
-      <c r="AR25" s="44"/>
-      <c r="AS25" s="44"/>
-      <c r="AT25" s="44"/>
-      <c r="AU25" s="44"/>
-      <c r="AV25" s="44"/>
-      <c r="AW25" s="26"/>
-      <c r="AX25" s="26"/>
-      <c r="AY25" s="26"/>
-      <c r="AZ25" s="26"/>
-      <c r="BA25" s="28"/>
-      <c r="BB25" s="25"/>
-      <c r="BC25" s="26"/>
-      <c r="BD25" s="26"/>
-      <c r="BE25" s="26"/>
-      <c r="BF25" s="26"/>
-      <c r="BG25" s="30"/>
-      <c r="BH25" s="30"/>
-      <c r="BI25" s="30"/>
-      <c r="BJ25" s="30"/>
-      <c r="BK25" s="30"/>
-      <c r="BL25" s="26"/>
-      <c r="BM25" s="26"/>
-      <c r="BN25" s="26"/>
-      <c r="BO25" s="26"/>
-      <c r="BP25" s="31"/>
-    </row>
-    <row r="26" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="57"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H26" s="70">
-        <v>0</v>
-      </c>
-      <c r="I26" s="65"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="26"/>
-      <c r="U26" s="26"/>
-      <c r="V26" s="26"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="25"/>
-      <c r="Y26" s="26"/>
-      <c r="Z26" s="26"/>
-      <c r="AA26" s="26"/>
-      <c r="AB26" s="26"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="26"/>
-      <c r="AI26" s="26"/>
-      <c r="AJ26" s="26"/>
-      <c r="AK26" s="26"/>
-      <c r="AL26" s="28"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="26"/>
-      <c r="AO26" s="26"/>
-      <c r="AP26" s="26"/>
-      <c r="AQ26" s="26"/>
-      <c r="AR26" s="44"/>
-      <c r="AS26" s="44"/>
-      <c r="AT26" s="44"/>
-      <c r="AU26" s="44"/>
-      <c r="AV26" s="44"/>
-      <c r="AW26" s="26"/>
-      <c r="AX26" s="26"/>
-      <c r="AY26" s="26"/>
-      <c r="AZ26" s="26"/>
-      <c r="BA26" s="28"/>
-      <c r="BB26" s="25"/>
-      <c r="BC26" s="26"/>
-      <c r="BD26" s="26"/>
-      <c r="BE26" s="26"/>
-      <c r="BF26" s="26"/>
-      <c r="BG26" s="30"/>
-      <c r="BH26" s="30"/>
-      <c r="BI26" s="30"/>
-      <c r="BJ26" s="30"/>
-      <c r="BK26" s="30"/>
-      <c r="BL26" s="26"/>
-      <c r="BM26" s="26"/>
-      <c r="BN26" s="26"/>
-      <c r="BO26" s="26"/>
-      <c r="BP26" s="31"/>
-    </row>
-    <row r="27" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="57"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H27" s="70">
-        <v>0</v>
-      </c>
-      <c r="I27" s="65"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="26"/>
-      <c r="T27" s="26"/>
-      <c r="U27" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="V27" s="26"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AE27" s="29"/>
-      <c r="AF27" s="29"/>
-      <c r="AG27" s="29"/>
-      <c r="AH27" s="26"/>
-      <c r="AI27" s="26"/>
-      <c r="AJ27" s="26"/>
-      <c r="AK27" s="26"/>
-      <c r="AL27" s="28"/>
-      <c r="AM27" s="25"/>
-      <c r="AN27" s="26"/>
-      <c r="AO27" s="26"/>
-      <c r="AP27" s="26"/>
-      <c r="AQ27" s="26"/>
-      <c r="AR27" s="44"/>
-      <c r="AS27" s="44"/>
-      <c r="AT27" s="44"/>
-      <c r="AU27" s="44"/>
-      <c r="AV27" s="44"/>
-      <c r="AW27" s="26"/>
-      <c r="AX27" s="26"/>
-      <c r="AY27" s="26"/>
-      <c r="AZ27" s="26"/>
-      <c r="BA27" s="28"/>
-      <c r="BB27" s="25"/>
-      <c r="BC27" s="26"/>
-      <c r="BD27" s="26"/>
-      <c r="BE27" s="26"/>
-      <c r="BF27" s="26"/>
-      <c r="BG27" s="30"/>
-      <c r="BH27" s="30"/>
-      <c r="BI27" s="30"/>
-      <c r="BJ27" s="30"/>
-      <c r="BK27" s="30"/>
-      <c r="BL27" s="26"/>
-      <c r="BM27" s="26"/>
-      <c r="BN27" s="26"/>
-      <c r="BO27" s="26"/>
-      <c r="BP27" s="31"/>
-    </row>
-    <row r="28" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="53">
-        <v>3.3</v>
-      </c>
-      <c r="C28" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" s="55"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H28" s="70">
-        <v>0</v>
-      </c>
-      <c r="I28" s="65"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="29"/>
-      <c r="AD28" s="29"/>
-      <c r="AE28" s="29"/>
-      <c r="AF28" s="29"/>
-      <c r="AG28" s="29"/>
-      <c r="AH28" s="26"/>
-      <c r="AI28" s="26"/>
-      <c r="AJ28" s="26"/>
-      <c r="AK28" s="26"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="25"/>
-      <c r="AN28" s="26"/>
-      <c r="AO28" s="26"/>
-      <c r="AP28" s="26"/>
-      <c r="AQ28" s="26"/>
-      <c r="AR28" s="44"/>
-      <c r="AS28" s="44"/>
-      <c r="AT28" s="44"/>
-      <c r="AU28" s="44"/>
-      <c r="AV28" s="44"/>
-      <c r="AW28" s="26"/>
-      <c r="AX28" s="26"/>
-      <c r="AY28" s="26"/>
-      <c r="AZ28" s="26"/>
-      <c r="BA28" s="28"/>
-      <c r="BB28" s="25"/>
-      <c r="BC28" s="26"/>
-      <c r="BD28" s="26"/>
-      <c r="BE28" s="26"/>
-      <c r="BF28" s="26"/>
-      <c r="BG28" s="30"/>
-      <c r="BH28" s="30"/>
-      <c r="BI28" s="30"/>
-      <c r="BJ28" s="30"/>
-      <c r="BK28" s="30"/>
-      <c r="BL28" s="26"/>
-      <c r="BM28" s="26"/>
-      <c r="BN28" s="26"/>
-      <c r="BO28" s="26"/>
-      <c r="BP28" s="31"/>
-    </row>
-    <row r="29" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="57"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H29" s="70">
-        <v>0</v>
-      </c>
-      <c r="I29" s="65"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
-      <c r="AG29" s="29"/>
-      <c r="AH29" s="26"/>
-      <c r="AI29" s="26"/>
-      <c r="AJ29" s="26"/>
-      <c r="AK29" s="26"/>
-      <c r="AL29" s="28"/>
-      <c r="AM29" s="25"/>
-      <c r="AN29" s="26"/>
-      <c r="AO29" s="26"/>
-      <c r="AP29" s="26"/>
-      <c r="AQ29" s="26"/>
-      <c r="AR29" s="44"/>
-      <c r="AS29" s="44"/>
-      <c r="AT29" s="44"/>
-      <c r="AU29" s="44"/>
-      <c r="AV29" s="44"/>
-      <c r="AW29" s="26"/>
-      <c r="AX29" s="26"/>
-      <c r="AY29" s="26"/>
-      <c r="AZ29" s="26"/>
-      <c r="BA29" s="28"/>
-      <c r="BB29" s="25"/>
-      <c r="BC29" s="26"/>
-      <c r="BD29" s="26"/>
-      <c r="BE29" s="26"/>
-      <c r="BF29" s="26"/>
-      <c r="BG29" s="30"/>
-      <c r="BH29" s="30"/>
-      <c r="BI29" s="30"/>
-      <c r="BJ29" s="30"/>
-      <c r="BK29" s="30"/>
-      <c r="BL29" s="26"/>
-      <c r="BM29" s="26"/>
-      <c r="BN29" s="26"/>
-      <c r="BO29" s="26"/>
-      <c r="BP29" s="31"/>
-    </row>
-    <row r="30" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="53">
-        <v>4</v>
-      </c>
-      <c r="C30" s="58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="59"/>
-      <c r="E30" s="81"/>
-      <c r="F30" s="78"/>
-      <c r="G30" s="60" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H30" s="71"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="22"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="22"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="23"/>
-      <c r="X30" s="21"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="22"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="22"/>
-      <c r="AC30" s="22"/>
-      <c r="AD30" s="22"/>
-      <c r="AE30" s="22"/>
-      <c r="AF30" s="22"/>
-      <c r="AG30" s="22"/>
-      <c r="AH30" s="22"/>
-      <c r="AI30" s="22"/>
-      <c r="AJ30" s="22"/>
-      <c r="AK30" s="22"/>
-      <c r="AL30" s="23"/>
-      <c r="AM30" s="21"/>
-      <c r="AN30" s="22"/>
-      <c r="AO30" s="22"/>
-      <c r="AP30" s="22"/>
-      <c r="AQ30" s="22"/>
-      <c r="AR30" s="22"/>
-      <c r="AS30" s="22"/>
-      <c r="AT30" s="22"/>
-      <c r="AU30" s="22"/>
-      <c r="AV30" s="22"/>
-      <c r="AW30" s="22"/>
-      <c r="AX30" s="22"/>
-      <c r="AY30" s="22"/>
-      <c r="AZ30" s="22"/>
-      <c r="BA30" s="23"/>
-      <c r="BB30" s="21"/>
-      <c r="BC30" s="22"/>
-      <c r="BD30" s="22"/>
-      <c r="BE30" s="22"/>
-      <c r="BF30" s="22"/>
-      <c r="BG30" s="22"/>
-      <c r="BH30" s="22"/>
-      <c r="BI30" s="22"/>
-      <c r="BJ30" s="22"/>
-      <c r="BK30" s="22"/>
-      <c r="BL30" s="22"/>
-      <c r="BM30" s="22"/>
-      <c r="BN30" s="22"/>
-      <c r="BO30" s="22"/>
-      <c r="BP30" s="24"/>
-    </row>
-    <row r="31" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="53">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="55"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H31" s="70">
-        <v>0</v>
-      </c>
-      <c r="I31" s="65"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="28"/>
-      <c r="X31" s="25"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="29"/>
-      <c r="AD31" s="29"/>
-      <c r="AE31" s="29"/>
-      <c r="AF31" s="29"/>
-      <c r="AG31" s="29"/>
-      <c r="AH31" s="26"/>
-      <c r="AI31" s="26"/>
-      <c r="AJ31" s="26"/>
-      <c r="AK31" s="26"/>
-      <c r="AL31" s="28"/>
-      <c r="AM31" s="25"/>
-      <c r="AN31" s="26"/>
-      <c r="AO31" s="26"/>
-      <c r="AP31" s="26"/>
-      <c r="AQ31" s="26"/>
-      <c r="AR31" s="44"/>
-      <c r="AS31" s="44"/>
-      <c r="AT31" s="44"/>
-      <c r="AU31" s="44"/>
-      <c r="AV31" s="44"/>
-      <c r="AW31" s="26"/>
-      <c r="AX31" s="26"/>
-      <c r="AY31" s="26"/>
-      <c r="AZ31" s="26"/>
-      <c r="BA31" s="28"/>
-      <c r="BB31" s="25"/>
-      <c r="BC31" s="75"/>
-      <c r="BD31" s="26"/>
-      <c r="BE31" s="26"/>
-      <c r="BF31" s="26"/>
-      <c r="BG31" s="30"/>
-      <c r="BH31" s="30"/>
-      <c r="BI31" s="30"/>
-      <c r="BJ31" s="30"/>
-      <c r="BK31" s="30"/>
-      <c r="BL31" s="26"/>
-      <c r="BM31" s="26"/>
-      <c r="BN31" s="26"/>
-      <c r="BO31" s="26"/>
-      <c r="BP31" s="31"/>
-    </row>
-    <row r="32" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="53">
-        <v>4.2</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D32" s="55"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H32" s="70">
-        <v>0</v>
-      </c>
-      <c r="I32" s="65"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="26"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="25"/>
-      <c r="Y32" s="26"/>
-      <c r="Z32" s="26"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
-      <c r="AG32" s="29"/>
-      <c r="AH32" s="26"/>
-      <c r="AI32" s="26"/>
-      <c r="AJ32" s="26"/>
-      <c r="AK32" s="26"/>
-      <c r="AL32" s="28"/>
-      <c r="AM32" s="25"/>
-      <c r="AN32" s="26"/>
-      <c r="AO32" s="26"/>
-      <c r="AP32" s="26"/>
-      <c r="AQ32" s="26"/>
-      <c r="AR32" s="44"/>
-      <c r="AS32" s="44"/>
-      <c r="AT32" s="44"/>
-      <c r="AU32" s="44"/>
-      <c r="AV32" s="44"/>
-      <c r="AW32" s="26"/>
-      <c r="AX32" s="26"/>
-      <c r="AY32" s="26"/>
-      <c r="AZ32" s="26"/>
-      <c r="BA32" s="28"/>
-      <c r="BB32" s="25"/>
-      <c r="BC32" s="26"/>
-      <c r="BD32" s="26"/>
-      <c r="BE32" s="26"/>
-      <c r="BF32" s="26"/>
-      <c r="BG32" s="30"/>
-      <c r="BH32" s="30"/>
-      <c r="BI32" s="30"/>
-      <c r="BJ32" s="30"/>
-      <c r="BK32" s="30"/>
-      <c r="BL32" s="26"/>
-      <c r="BM32" s="26"/>
-      <c r="BN32" s="26"/>
-      <c r="BO32" s="26"/>
-      <c r="BP32" s="31"/>
-    </row>
-    <row r="33" spans="2:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="53">
-        <v>4.3</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="55"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H33" s="70">
-        <v>0</v>
-      </c>
-      <c r="I33" s="65"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="26"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="26"/>
-      <c r="V33" s="26"/>
-      <c r="W33" s="28"/>
-      <c r="X33" s="25"/>
-      <c r="Y33" s="26"/>
-      <c r="Z33" s="26"/>
-      <c r="AA33" s="26"/>
-      <c r="AB33" s="26"/>
-      <c r="AC33" s="29"/>
-      <c r="AD33" s="29"/>
-      <c r="AE33" s="29"/>
-      <c r="AF33" s="29"/>
-      <c r="AG33" s="29"/>
-      <c r="AH33" s="26"/>
-      <c r="AI33" s="26"/>
-      <c r="AJ33" s="26"/>
-      <c r="AK33" s="26"/>
-      <c r="AL33" s="28"/>
-      <c r="AM33" s="25"/>
-      <c r="AN33" s="26"/>
-      <c r="AO33" s="26"/>
-      <c r="AP33" s="26"/>
-      <c r="AQ33" s="26"/>
-      <c r="AR33" s="44"/>
-      <c r="AS33" s="44"/>
-      <c r="AT33" s="44"/>
-      <c r="AU33" s="44"/>
-      <c r="AV33" s="44"/>
-      <c r="AW33" s="26"/>
-      <c r="AX33" s="26"/>
-      <c r="AY33" s="26"/>
-      <c r="AZ33" s="26"/>
-      <c r="BA33" s="28"/>
-      <c r="BB33" s="25"/>
-      <c r="BC33" s="26"/>
-      <c r="BD33" s="26"/>
-      <c r="BE33" s="26"/>
-      <c r="BF33" s="26"/>
-      <c r="BG33" s="30"/>
-      <c r="BH33" s="30"/>
-      <c r="BI33" s="30"/>
-      <c r="BJ33" s="30"/>
-      <c r="BK33" s="30"/>
-      <c r="BL33" s="26"/>
-      <c r="BM33" s="26"/>
-      <c r="BN33" s="26"/>
-      <c r="BO33" s="26"/>
-      <c r="BP33" s="31"/>
-    </row>
-    <row r="34" spans="2:68" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="63"/>
-      <c r="E34" s="82"/>
-      <c r="F34" s="84"/>
-      <c r="G34" s="86" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="H34" s="72">
-        <v>0</v>
-      </c>
-      <c r="I34" s="66"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="37"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="35"/>
-      <c r="Z34" s="35"/>
-      <c r="AA34" s="35"/>
-      <c r="AB34" s="35"/>
-      <c r="AC34" s="38"/>
-      <c r="AD34" s="38"/>
-      <c r="AE34" s="38"/>
-      <c r="AF34" s="38"/>
-      <c r="AG34" s="38"/>
-      <c r="AH34" s="35"/>
-      <c r="AI34" s="35"/>
-      <c r="AJ34" s="35"/>
-      <c r="AK34" s="35"/>
-      <c r="AL34" s="37"/>
-      <c r="AM34" s="34"/>
-      <c r="AN34" s="35"/>
-      <c r="AO34" s="35"/>
-      <c r="AP34" s="35"/>
-      <c r="AQ34" s="35"/>
-      <c r="AR34" s="45"/>
-      <c r="AS34" s="45"/>
-      <c r="AT34" s="45"/>
-      <c r="AU34" s="45"/>
-      <c r="AV34" s="45"/>
-      <c r="AW34" s="35"/>
-      <c r="AX34" s="35"/>
-      <c r="AY34" s="35"/>
-      <c r="AZ34" s="35"/>
-      <c r="BA34" s="37"/>
-      <c r="BB34" s="34"/>
-      <c r="BC34" s="35"/>
-      <c r="BD34" s="35"/>
-      <c r="BE34" s="35"/>
-      <c r="BF34" s="35"/>
-      <c r="BG34" s="39"/>
-      <c r="BH34" s="39"/>
-      <c r="BI34" s="39"/>
-      <c r="BJ34" s="39"/>
-      <c r="BK34" s="39"/>
-      <c r="BL34" s="35"/>
-      <c r="BM34" s="35"/>
-      <c r="BN34" s="35"/>
-      <c r="BO34" s="35"/>
-      <c r="BP34" s="40"/>
-    </row>
-    <row r="41" spans="2:68" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="C41" s="3"/>
+    <row r="28" spans="2:68" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="C28" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -6842,8 +5994,8 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:H4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H10:H34">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="H10:H21">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="percent" val="0"/>
         <cfvo type="percent" val="100"/>
@@ -6858,9 +6010,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="119" scale="59" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="B34" numberStoredAsText="1"/>
-  </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6877,7 +6026,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>H10:H34</xm:sqref>
+          <xm:sqref>H10:H21</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6893,13 +6042,13 @@
   <dimension ref="B2"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.375" style="91" customWidth="1"/>
-    <col min="2" max="2" width="88.375" style="91" customWidth="1"/>
-    <col min="3" max="16384" width="10.875" style="91"/>
+    <col min="1" max="1" width="3.375" style="89" customWidth="1"/>
+    <col min="2" max="2" width="88.375" style="89" customWidth="1"/>
+    <col min="3" max="16384" width="10.875" style="89"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="90" t="s">
         <v>70</v>
       </c>
     </row>
